--- a/clients/luxhomme/seo/meta-plan-2026-10.xlsx
+++ b/clients/luxhomme/seo/meta-plan-2026-10.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статьи — description" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статьи — title" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1166,4 +1167,1374 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Статья (H1 — без изменений)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title сейчас</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Символов</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Новый SEO-title (Yoast)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Символов</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Вертикальный, моющий и компактный пылесос: в чём разница и как выбрать</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/vertikalnyj-moyushhij-i-kompaktnyj-pylesos-v-chyom-raznitsa-i-kak-vybrat</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Вертикальный, моющий и компактный пылесос: в чём разница и как выбрать | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Вертикальный, моющий или компактный пылесос | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Какая бытовая техника действительно экономит время дома</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kakaya-bytovaya-tehnika-dejstvitelno-ekonomit-vremya-doma</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Какая бытовая техника действительно экономит время дома | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Какая бытовая техника правда экономит время | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа или беговая дорожка: что лучше для домашних тренировок</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/vibroplatforma-ili-begovaya-dorozhka-chto-luchshe-dlya-domashnih-trenirovok</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа или беговая дорожка: что лучше для домашних тренировок | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа или беговая дорожка: что лучше для дома | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Как правильно заниматься на виброплатформе новичку: упражнения и рекомендации</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kak-pravilno-zanimatsya-na-vibroplatforme-novichku-uprazhneniya-i-rekomendatsii</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Как правильно заниматься на виброплатформе новичку: упражнения и рекомендации | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Как заниматься на виброплатформе новичку | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Что можно готовить в аэрогриле каждый день: идеи для завтрака, обеда и ужина</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/chto-mozhno-gotovit-v-aerogrile-kazhdyj-den-idei-dlya-zavtraka-obeda-i-uzhina</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Что можно готовить в аэрогриле каждый день: идеи для завтрака, обеда и ужина | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Что готовить в аэрогриле каждый день: идеи | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль какого объёма выбрать для семьи из 2, 3 или 4 человек</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/aerogril-kakogo-obyoma-vybrat-dlya-semi-iz-2-3-ili-4-chelovek</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль какого объёма выбрать для семьи из 2, 3 или 4 человек | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Объём аэрогриля для семьи из 2, 3 или 4 человек | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Моющий или обычный вертикальный пылесос: что лучше выбрать</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/moyushhij-ili-obychnyj-vertikalnyj-pylesos-chto-luchshe-vybrat</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Моющий или обычный вертикальный пылесос: что лучше выбрать | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Моющий или обычный вертикальный пылесос: что выбрать | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать паровую швабру для квартиры и частного дома</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kak-vybrat-parovuyu-shvabru-dlya-kvartiry-i-chastnogo-doma</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать паровую швабру для квартиры и частного дома | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра для квартиры и частного дома | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли мыть ламинат паровой шваброй и как делать это правильно</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/mozhno-li-myt-laminat-parovoj-shvabroj-i-kak-delat-eto-pravilno</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли мыть ламинат паровой шваброй и как делать это правильно | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Можно ли мыть ламинат паровой шваброй | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра или моющий пылесос: что лучше выбрать для дома</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/parovaya-shvabra-ili-moyushhij-pylesos-chto-luchshe-vybrat-dlya-doma</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра или моющий пылесос: что лучше выбрать для дома | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра или моющий пылесос на каждый день | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Лучшие паровые швабры для дома: рейтинг моделей Luxhommè</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/luchshie-parovye-shvabry-dlya-doma-rejting-modelej-luxhomm</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Лучшие паровые швабры для дома: рейтинг моделей Luxhommè | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Лучшие паровые швабры для дома: рейтинг моделей | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Какую кофемашину выбрать для дома: советы и рекомендации</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kakuyu-kofemashinu-vybrat-dlya-doma-sovety-i-rekomendatsii</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Какую кофемашину выбрать для дома: советы и рекомендации | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Какую кофемашину выбрать для дома: советы | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Моющие пылесосы для мебели: как выбрать и правильно использовать</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/moyushhie-pylesosy-dlya-mebeli-kak-vybrat-i-pravilno-ispolzovat</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Моющие пылесосы для мебели: как выбрать и правильно использовать | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Моющий пылесос для мебели: как выбрать | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Лучшие вертикальные пылесосы для дома: как выбрать подходящую модель</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/luchshie-vertikalnye-pylesosy-dlya-doma-kak-vybrat-podhodyashhuyu-model</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Лучшие вертикальные пылесосы для дома: как выбрать подходящую модель | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Лучшие вертикальные пылесосы для дома: как выбрать | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина 4 в 1: зачем нужна поддержка разных капсул и молотого кофе</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kofemashina-4-v-1</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина 4 в 1: зачем нужна поддержка разных капсул и молотого кофе | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина 4 в 1: капсулы разных систем и молотый кофе | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Как приготовить капучино дома без большой автоматической кофемашины</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kak-prigotovit-kapuchino-doma</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Как приготовить капучино дома без большой автоматической кофемашины | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Как приготовить капучино дома без большой кофемашины | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Эспрессо, лунго и американо: чем отличаются популярные кофейные напитки</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/espresso-lungo-americano-otlichiya</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Эспрессо, лунго и американо: чем отличаются популярные кофейные напитки | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Эспрессо, лунго и американо: в чём разница | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Как ухаживать за капсульной кофемашиной и сохранить вкус кофе</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/uhod-za-kapsulnoy-kofemashinoy</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Как ухаживать за капсульной кофемашиной и сохранить вкус кофе | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Уход за капсульной кофемашиной: чистка и вкус кофе | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина для маленькой кухни: как выбрать компактную технику без лишних функций</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kofemashina-dlya-malenkoy-kuhni</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина для маленькой кухни: как выбрать компактную технику без лишних функций | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Компактная кофемашина для маленькой кухни | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра: что можно и что нельзя очищать горячим паром</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/parovaya-shvabra-chto-mozhno-chistit</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра: что можно и что нельзя очищать горячим паром | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Что можно и нельзя чистить паровой шваброй | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Как убрать кухню с помощью пара и уменьшить количество бытовой химии</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/uborka-kuhni-parom</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Как убрать кухню с помощью пара и уменьшить количество бытовой химии | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Уборка кухни паром без лишней бытовой химии | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Генеральная уборка квартиры за один день: пошаговый план без хаоса</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/plan-generalnoy-uborki-kvartiry</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Генеральная уборка квартиры за один день: пошаговый план без хаоса | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Генеральная уборка за один день: пошаговый план | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать вертикальный пылесос для дома с кошкой или собакой</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/vertikalnyy-pylesos-dlya-doma-s-zhivotnymi</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать вертикальный пылесос для дома с кошкой или собакой | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Вертикальный пылесос для дома с кошкой или собакой | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать пылесос для ламината и плитки: сухая или влажная уборка</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/pylesos-dlya-laminata-i-plitki</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать пылесос для ламината и плитки: сухая или влажная уборка | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Пылесос для ламината и плитки: сухой или моющий | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Как очистить межплиточные швы паром и не повредить поверхность</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/ochistka-mezhplitochnyh-shvov-parom</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Как очистить межплиточные швы паром и не повредить поверхность | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Как очистить межплиточные швы паром | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать виброплатформу для дома: 7 параметров перед покупкой</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kak-vybrat-vibroplatformu-dlya-doma</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать виброплатформу для дома: 7 параметров перед покупкой | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать виброплатформу: 7 параметров | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа для начинающих: как построить первые домашние тренировки</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/pervye-trenirovki-na-vibroplatforme-doma</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа для начинающих: как построить первые домашние тренировки | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа для начинающих: первые тренировки | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2D или 3D виброплатформа: в чём разница и какую выбрать</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/2d-ili-3d-vibroplatforma-raznica</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2D или 3D виброплатформа: в чём разница и какую выбрать | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2D или 3D виброплатформа: в чём разница | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа с EMS: что это такое и как использовать функцию безопасно</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/vibroplatforma-s-ems-kak-rabotaet</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа с EMS: что это такое и как использовать функцию безопасно | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа с EMS: как работает и безопасность | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Домашняя тренировка на виброплатформе за 15 минут: простой комплекс</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/trenirovka-na-vibroplatforme-15-minut</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Домашняя тренировка на виброплатформе за 15 минут: простой комплекс | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Тренировка на виброплатформе за 15 минут | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Капсульная кофемашина для дома: как выбрать удобную модель</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kapsulnaya-kofemashina-dlya-doma</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Капсульная кофемашина для дома: как выбрать удобную модель | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Капсульная кофемашина для дома: как выбрать | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Как правильно разогревать еду в аэрогриле: пицца, выпечка, мясо и картофель</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kak-razogrevat-edu-v-aerogrile</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Как правильно разогревать еду в аэрогриле: пицца, выпечка, мясо и картофель | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Как разогревать еду в аэрогриле: пицца, мясо, выпечка | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Как ухаживать за аэрогрилем, чтобы он дольше оставался чистым</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kak-uhazhivat-za-aerogrilem</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Как ухаживать за аэрогрилем, чтобы он дольше оставался чистым | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Уход за аэрогрилем: как сохранить его чистым | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Какой объём аэрогриля выбрать для одного человека, пары и семьи</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kakoy-obem-aerogrilya-vybrat</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Какой объём аэрогриля выбрать для одного человека, пары и семьи | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Какой объём аэрогриля выбрать: от 1 человека до семьи | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Как готовить в аэрогриле почти без масла и сохранять вкус продуктов</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/aerogril-bez-masla</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Как готовить в аэрогриле почти без масла и сохранять вкус продуктов | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Как готовить в аэрогриле почти без масла | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль или мультиварка: какой прибор полезнее на кухне</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/aerogril-ili-multivarka</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль или мультиварка: какой прибор полезнее на кухне | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль или мультиварка: что полезнее на кухне | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль или духовка: что лучше для повседневной готовки</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/aerogril-ili-duhovka</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль или духовка: что лучше для повседневной готовки | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль или духовка для повседневной готовки | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Что можно готовить в аэрогриле: 15 идей для завтрака, обеда и ужина</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/chto-prigotovit-v-aerogrile</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Что можно готовить в аэрогриле: 15 идей для завтрака, обеда и ужина | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Что приготовить в аэрогриле: 15 идей | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать паровую швабру для ламината, плитки и ковров</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kak-vybrat-parovuyu-shvabru</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать паровую швабру для ламината, плитки и ковров | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра для ламината, плитки и ковров | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль с одной или двумя чашами: какой вариант выбрать</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/aerogril-odna-ili-dve-chashi</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль с одной или двумя чашами: какой вариант выбрать | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль с одной или двумя чашами: что выбрать | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать аэрогриль для дома: объём, мощность и программы</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/kak-vybrat-aerogril-dlya-doma</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать аэрогриль для дома: объём, мощность и программы | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Как выбрать аэрогриль: объём, мощность, программы | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Новинки Luxhommè, которые заботятся о вас и вашем доме</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/novinki-luxhomm-kotorye-zabotyatsya-o-vas-i-vashem-dome</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Новинки Luxhommè, которые заботятся о вас и вашем доме | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Новинки техники, которые заботятся о вас и доме | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Новые продукты Luxhommè</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/novye-produkty-luxhomme-tehnika-dlya-vdohno</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Новые продукты Luxhommè | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Новые продукты: техника для дома и кухни | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Философия Уюта</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/filosofiya-uyuta-kak-luxhomme-pomogaet-zabot</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Философия Уюта | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Философия уюта: техника, которая бережёт время | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Ритуалы для каждого</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/ritualy-dlya-zhenshhin-kak-luxhomme-vdohnovlyae</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Ритуалы для каждого | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>10 домашних ритуалов заботы о себе | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Продукты Luxhommè</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/produkty-luxhomme-tehnika-dlya-uyuta-i-zaboty</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Продукты Luxhommè | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Серии техники для дома: кухня, чистота и забота | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Luxhommè — Техника для Дома, Которая Освобождает от Забот</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog/luxhomme-tehnika-dlya-doma-kotoraya-osvobozhd</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Luxhommè — Техника для Дома, Которая Освобождает от Забот | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Техника для дома, которая освобождает от забот | Luxhommè</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clients/luxhomme/seo/meta-plan-2026-10.xlsx
+++ b/clients/luxhomme/seo/meta-plan-2026-10.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статьи — description" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статьи — title" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2537,4 +2538,823 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Товар (H1)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title сейчас</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Симв.</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Короткое название для шаблона</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Новый title (цена подставляется сайтом)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Симв.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Description сейчас</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Симв.</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Новый description</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Симв.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина автоматическая зерновая с капучинатором и кофемолкой CremaX</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/cremax</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Купить кофемашину автоматическую зерновую с капучинатором и кофемолкой CremaX — 24 290 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина CremaX с кофемолкой</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина CremaX с кофемолкой — купить, цена 24 290 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Купить кофемашину автоматическую зерновую с капучинатором и кофемолкой CremaX — 24 290 ₽. Рожковая кофемашина LUXHOMME CremaX со встроенной кофемолкой — кофе как в кофейне, но у вас дома. Одна машина заменяет к</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина CremaX 5 в 1 со встроенной кофемолкой: зёрна, молотый кофе, капсулы Nespresso и Dolce Gusto, ESE. 10 программ, два капучинатора, холодный кофе.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина рожковая Luxhommè Caffio Professional</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/caffio-professional</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Купить кофемашину рожковую Luxhommè Caffio Professional — 16 597 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина Caffio Professional</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина Caffio Professional — купить, цена 16 597 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Купить кофемашину рожковую Luxhommè Caffio Professional — 16 597 ₽. Кофемашина рожковая Luxhommè Caffio Professional объединяет четыре формата приготовления кофе и помогает выбрать подходя</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Рожковая кофемашина Caffio Professional 4 в 1: молотый кофе, капсулы, ESE. Помпа ULKA, нагрев от 10 секунд, капучинатор, горячие и холодные напитки.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа для похудения 3D c EMS токами и нагревом, нагрузка до 150 кг</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/vibroplatforma-dlya-pohudeniya-3d-c-ems-tokami-i-nagrevom-do-150-kg</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Купить виброплатформу длю похудению 3D c EMS токами и нагревом, нагрузка до 150 кг — 16 100 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа 3D с EMS и прогревом</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа 3D с EMS и прогревом — купить, цена 16 100 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Купить виброплатформу длю похудению 3D c EMS токами и нагревом, нагрузка до 150 кг — 16 100 ₽. Виброплатформа 3D с EMS-токами и функцией нагрева — многофункциональный тренажёр для домашних тренировок. Она сочетает в</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа 3D с EMS и прогревом для тренировок дома: 400 Вт, нагрузка до 150 кг, регулировка интенсивности. Мышцы ног, ягодиц, пресса, спины и рук.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль Luxhommè AirChef Dual Pro (2 чаши)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/airgrill-dual-pro</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Купить аэрогриль Luxhommè AirChef Dual Pro (2 чаши) — 16 075 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль с 2 чашами AirChef Dual Pro</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль с 2 чашами AirChef Dual Pro — купить, цена 16 075 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Купить аэрогриль Luxhommè AirChef Dual Pro (2 чаши) — 16 075 ₽. Аэрогриль Luxhommè AirChef Dual Pro — это две независимые камеры в одном корпусе. Верхняя чаша на 7 литров и нижняя на 5</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>184</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль AirChef Dual Pro: две независимые чаши 7 и 5 л, своя температура и программа у каждой, 3200 Вт. Мясо и гарнир одновременно, почти без масла.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Вертикальный сухой пылесос Aerlyn</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/vertikalnyj-suhoj-pylesos-aerlyn</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Купить вертикальный сухой пылесос Aerlyn — 15 471 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Вертикальный пылесос Aerlyn</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Вертикальный пылесос Aerlyn — купить, цена 15 471 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Купить вертикальный сухой пылесос Aerlyn — 15 471 ₽. Aerlyn берёт на себя и сухую, и влажную уборку. Один беспроводной вертикальный пылесос заменяет обычный пылесос, турбощё</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Беспроводной вертикальный пылесос Aerlyn: мотор 420 Вт, 4 режима и авторежим, турбощётка для шерсти. Плитка, ламинат и ковры, насадка для влажной уборки.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Вертикальный моющий пылесос Aqvion Pro</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/vertikalnyj-moyushhij-pylesos-aqvion-pro</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Купить вертикальный моющий пылесос Aqvion Pro — 17 990 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Моющий пылесос Aqvion Pro</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Моющий пылесос Aqvion Pro — купить, цена 17 990 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Купить вертикальный моющий пылесос Aqvion Pro — 17 990 ₽. Aqvion Pro моет и пылесосит за один проход. Этот беспроводной моющий пылесос закрывает работу сразу трёх приборов — пыле</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Беспроводной моющий пылесос Aqvion Pro: моет и пылесосит за один проход, раздельные баки для чистой и грязной воды, уборка без бытовой химии.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Компактный моющий пылесос Cleneo Pro</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/kompaktnyj-moyushhij-pylesos-cleneo-pro</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Купить компактный моющий пылесос Cleneo Pro — 16 790 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Моющий пылесос Cleneo Pro</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Моющий пылесос Cleneo Pro — купить, цена 16 790 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Купить компактный моющий пылесос Cleneo Pro — 16 790 ₽. Cleneo Pro — компактный моющий пылесос для дома и автомобиля. Один прибор наводит порядок на полах, коврах и мебели, а з</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Компактный моющий пылесос Cleneo Pro с паром для дома и авто: чистка дивана, ковров и салона машины. 1400 Вт, пар или распыление воды, 13 насадок.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра Luxhommè AirSteam Pro</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/steamly-pro</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Купить паровую швабру Luxhommè AirSteam Pro — 10 990 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра AirSteam Pro</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра AirSteam Pro — купить, цена 10 990 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Купить паровую швабру Luxhommè AirSteam Pro — 10 990 ₽. Паровая швабра AirSteam Pro убирает горячим паром, а не химией: вода превращается в пар, который снимает грязь и жир с п</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра AirSteam Pro: 1800 Вт, пар до 150 °C уже через 30 секунд, 25 насадок для пола, окон, кухни, мебели и плитки, отпаривание одежды.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа uFit 2D Pro с EMS токами</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/ufit-2d-ems</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Купить виброплатформу uFit 2D Pro с EMS токами — 7 090 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа uFit 2D Pro EMS</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа uFit 2D Pro EMS — купить, цена 7 090 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Купить виброплатформу uFit 2D Pro с EMS токами — 7 090 ₽. Виброплатформа uFit 2D Pro — домашний тренажёр с вибрацией, функцией EMS и подогревом поверхности. Она рассчитана на кор</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа uFit 2D Pro для дома: вибрация, EMS и подогрев поверхности, регулировка интенсивности и программы. Тонус ног, пресса, спины и ягодиц.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра Luxhommè SC-100 Max</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/sc-100</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Купить паровую швабру Luxhommè SC-100 Max — 7 640 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра SC-100 Max</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра SC-100 Max — купить, цена 7 640 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Купить паровую швабру Luxhommè SC-100 Max — 7 640 ₽. Паровая швабра SC-100 Max наводит порядок во всём доме силой горячего пара. Меняешь насадку — меняется и интенсивность п</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>173</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра SC-100 Max: своя подача пара под каждую насадку, от бережной до интенсивной. Моет линолеум, ламинат, паркет и кварцвинил без бытовой химии.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа uFit 2D Standard</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/ufit-2d</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Купить виброплатформу uFit 2D Standard — 5 716 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа uFit 2D Standard</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Виброплатформа uFit 2D Standard — купить, цена 5 716 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Купить виброплатформу uFit 2D Standard — 5 716 ₽. Виброплатформа uFit 2D Standard — компактный домашний тренажёр для тех, кто хочет держать себя в тонусе без похода в зал</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Компактная виброплатформа uFit 2D Standard для тренировок дома: 5 программ, 180 скоростей, режимы бега и ходьбы. Тонус ног, пресса, спины и рук.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра Luxhommè EcoSteam Pro</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/ecosteam-pro</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Купить паровую швабру Luxhommè EcoSteam Pro — 5 671 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра EcoSteam Pro</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра EcoSteam Pro — купить, цена 5 671 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Купить паровую швабру Luxhommè EcoSteam Pro — 5 671 ₽. Паровая швабра EcoSteam Pro убирает горячим паром аккуратно и экономно. Парогенератор доводит воду до пара всего за 30 с</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Паровая швабра EcoSteam Pro: пар через 30 секунд, до 120 °C, подача 30 г/мин. Поворотная головка 270° и 22 насадки для пола, плитки, ковров и углов.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина Luxhommè CoffeeMaker Classic</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/coffee</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Купить кофемашину Luxhommè CoffeeMaker Classic — 9 290 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина 4 в 1 CoffeeMaker Classic</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Кофемашина 4 в 1 CoffeeMaker Classic — купить, цена 9 290 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Купить кофемашину Luxhommè CoffeeMaker Classic — 9 290 ₽. Капсульная кофемашина Luxhommè Classic готовит насыщенный кофе дома нажатием кнопки. Помпа с давлением 19 бар как следуе</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Капсульная кофемашина CoffeeMaker Classic 4 в 1: капсулы Nespresso и Dolce Gusto, ESE и молотый кофе. Помпа 19 бар, капучинатор, горячие и холодные напитки.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль Luxhommè AirChef</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/airgrill</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Купить аэрогриль Luxhommè AirChef — 5 490 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль AirChef 5,5 л</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль AirChef 5,5 л — купить, цена 5 490 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Купить аэрогриль Luxhommè AirChef — 5 490 ₽. Аэрогриль Luxhommè AirChef готовит на горячем воздухе и заменяет на кухне до десяти приборов сразу — от духовки до фритю</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Аэрогриль AirChef 5,5 л с окошком: 12 программ, 35–200 °C, режим сушки, готовит без предварительного нагрева. Курица, рыба, овощи почти без масла.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Робот мойщик Luxhommè uClean Max</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/products/window</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Купить робот мойщик Luxhommè uClean Max — 9 990 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Робот-мойщик окон uClean Max</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Робот-мойщик окон uClean Max — купить, цена 9 990 ₽ | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Купить робот мойщик Luxhommè uClean Max — 9 990 ₽. Робот мойщик окон с двойным распылением от бренда LUXHOMME – чистота без усилий! Забудьте про утомительную мойку окон! У</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>171</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Робот-мойщик окон uClean Max: двойное распыление воды, вакуумная фиксация на стекле, автоматический и ручной режим. Моет окна снаружи и внутри.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>143</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/clients/luxhomme/seo/meta-plan-2026-10.xlsx
+++ b/clients/luxhomme/seo/meta-plan-2026-10.xlsx
@@ -2738,16 +2738,16 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Виброплатформа 3D с EMS и прогревом</t>
+          <t>Виброплатформа 3D с EMS, нагрев</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Виброплатформа 3D с EMS и прогревом — купить, цена 16 100 ₽ | Luxhommè</t>
+          <t>Виброплатформа 3D с EMS, нагрев — купить, цена 16 100 ₽ | Luxhommè</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -2787,16 +2787,16 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Аэрогриль с 2 чашами AirChef Dual Pro</t>
+          <t>Аэрогриль AirChef Dual Pro</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Аэрогриль с 2 чашами AirChef Dual Pro — купить, цена 16 075 ₽ | Luxhommè</t>
+          <t>Аэрогриль AirChef Dual Pro — купить, цена 16 075 ₽ | Luxhommè</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -3228,16 +3228,16 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Кофемашина 4 в 1 CoffeeMaker Classic</t>
+          <t>Кофемашина CoffeeMaker Classic</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Кофемашина 4 в 1 CoffeeMaker Classic — купить, цена 9 290 ₽ | Luxhommè</t>
+          <t>Кофемашина CoffeeMaker Classic — купить, цена 9 290 ₽ | Luxhommè</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>

--- a/clients/luxhomme/seo/meta-plan-2026-10.xlsx
+++ b/clients/luxhomme/seo/meta-plan-2026-10.xlsx
@@ -2738,16 +2738,16 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Виброплатформа 3D с EMS, нагрев</t>
+          <t>Виброплатформа 3D с EMS</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Виброплатформа 3D с EMS, нагрев — купить, цена 16 100 ₽ | Luxhommè</t>
+          <t>Виброплатформа 3D с EMS — купить, цена 16 100 ₽ | Luxhommè</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>

--- a/clients/luxhomme/seo/meta-plan-2026-10.xlsx
+++ b/clients/luxhomme/seo/meta-plan-2026-10.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статьи — description" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статьи — title" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Страницы" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3357,4 +3358,676 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Страница</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Где редактировать</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Title сейчас</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Симв.</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Новый title</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Симв.</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Description сейчас</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Симв.</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Новый description</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Симв.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>WordPress: luxhomme/v1/hero → seo</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Luxhommè — бытовая техника для жизни</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Luxhommè — бытовая техника для дома: уборка, кухня, забота</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Luxhommè — премиальная бытовая техника для дома: кухонная техника, техника для уборки, спорт и аксессуары. Доставка по всей России.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Luxhommè — техника для дома: паровые швабры, моющие пылесосы, аэрогрили, кофемашины и виброплатформы. Доставка по России, гарантия, служба заботы.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>/catalog</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/catalog</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Код витрины</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Каталог товаров | Luxhommè</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Каталог техники для дома: уборка, кухня, фитнес | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Бытовая техника Luxhommè — паровые швабры, кухонная техника, спорт и аксессуары.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Каталог Luxhommè: паровые швабры, вертикальные и моющие пылесосы, аэрогрили, кофемашины, виброплатформы и робот-мойщик окон. Цены и наличие на сайте.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>/blog</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/blog</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Код витрины</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Блог | Luxhommè</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Блог: советы по уборке, кухне и уходу за собой | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Статьи, новости и полезные материалы от Luxhommè.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Блог Luxhommè: как выбрать пылесос, паровую швабру, аэрогриль или кофемашину, рецепты для аэрогриля, уход за техникой и тренировки на виброплатформе.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>/about</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/about</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>WordPress: luxhomme/v1/page-about → seo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>О нас | Luxhommè</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>О бренде Luxhommè: философия и линейки Cook, Clean, Care</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Luxhommè — жить легко и красиво каждый день. Наша философия, разработка бытовой техники, линейки Cook, Clean и Care и забота о покупателях.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Luxhommè — жить легко и красиво каждый день. Философия бренда, как мы разрабатываем технику, линейки Cook, Clean и Care и забота о покупателях.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>/contact</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/contact</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>WordPress: luxhomme/v1/page-contact → seo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Контакты | Luxhommè</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Контакты: служба заботы, адрес, реквизиты | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Контактная информация Luxhommè: адрес, телефон, email, социальные сети.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Связаться с Luxhommè: email care@luxhomme.store, служба заботы в Telegram и MAX, режим работы 9:00–21:00 МСК, адрес и реквизиты компании в Казани.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>/buy</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/buy</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>WordPress: luxhomme/v1/page-buy → seo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Мы на маркетплейсах | Luxhommè</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Где купить: Ozon, Wildberries, Яндекс Маркет | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Покупайте продукцию Luxhommè на OZON, Wildberries, Яндекс Маркет и других маркетплейсах.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Техника Luxhommè на маркетплейсах: Ozon, Wildberries и Яндекс Маркет. Ссылки на официальные магазины бренда и покупка напрямую на сайте luxhomme.store.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>/delivery</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/delivery</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>WordPress: luxhomme/v1/page-delivery → seo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Доставка и оплата | Luxhommè</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Доставка и оплата по России | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Доставка Luxhommè через Ozon до двери или в ПВЗ: доступность и сроки по адресу, способы оплаты и документы.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Доставка Luxhommè через Ozon до двери или в пункт выдачи: сроки и доступность по вашему адресу, способы оплаты, документы и помощь службы заботы.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>/service</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/service</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>WordPress: luxhomme/v1/page-service → seo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Сервис и гарантия | Luxhommè</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Сервис и гарантия на технику | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Гарантийное обслуживание, возврат и обмен товаров Luxhommè. Условия, контакты сервисной службы.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Гарантия на технику Luxhommè: условия гарантийного обслуживания, возврат и обмен товара, как обратиться в сервисную службу и службу заботы.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>/returns</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/returns</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Код витрины</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Правила возврата товара | Luxhommè</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Возврат и обмен товара: условия и сроки | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Условия и порядок возврата товара надлежащего и ненадлежащего качества в интернет-магазине Luxhommè.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Как вернуть или обменять товар Luxhommè: условия возврата товара надлежащего и ненадлежащего качества, порядок действий и контакты службы заботы.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>/offer</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/offer</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Код витрины</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Публичная оферта | Luxhommè</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Публичная оферта интернет-магазина | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Публичная оферта интернет-магазина Luxhommè: условия заключения и исполнения договора купли-продажи.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Публичная оферта интернет-магазина Luxhommè: условия заключения и исполнения договора купли-продажи, оплата, доставка, возврат и ответственность сторон.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>/privacy</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/privacy</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Код витрины</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Политика конфиденциальности | Luxhommè</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Политика конфиденциальности | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Политика в отношении обработки персональных данных пользователей интернет-магазина Luxhommè.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Политика обработки персональных данных пользователей интернет-магазина Luxhommè: какие данные собираем, зачем, как храним и как отозвать согласие.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>/cookie</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://luxhomme.store/cookie</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Код витрины</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Политика использования файлов cookie | Luxhommè</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Политика использования cookie | Luxhommè</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Какие cookie использует сайт Luxhommè, как ими управлять и какие данные через них собираются.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Какие файлы cookie использует сайт Luxhommè, для чего они нужны, какие данные через них собираются и как управлять cookie в настройках браузера.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>